--- a/Simulation/energy details.xlsx
+++ b/Simulation/energy details.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MIT Dropbox\Wande Cairang\XJTU research\Mo-Nb\Simulations\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wande\Documents\GitHub\Nb-irradiated-Mo\Simulation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8602889D-4AB0-491D-92CD-F1EC1D8F7F3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6560FFEE-E5B9-4763-9586-96A3B3F48A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41750" yWindow="2990" windowWidth="28800" windowHeight="15370" xr2:uid="{94C7064E-809E-475A-B3EA-883B2D7F657F}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{94C7064E-809E-475A-B3EA-883B2D7F657F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>X+Slab_Mo</t>
   </si>
@@ -86,13 +86,16 @@
     <t>1 Nb</t>
   </si>
   <si>
-    <t xml:space="preserve">Adorption energy </t>
-  </si>
-  <si>
     <t>100 surface</t>
   </si>
   <si>
     <t>110 surface</t>
+  </si>
+  <si>
+    <t>Adorption energy for 100</t>
+  </si>
+  <si>
+    <t>Adorption energy for 110</t>
   </si>
 </sst>
 </file>
@@ -486,16 +489,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" t="s">
         <v>11</v>
       </c>
       <c r="C1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>17</v>
+      </c>
+      <c r="E1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
